--- a/artfynd/A 14594-2022 artfynd.xlsx
+++ b/artfynd/A 14594-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ17"/>
+  <dimension ref="A1:AZ20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1679,27 +1679,27 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129642515</v>
+        <v>136808909</v>
       </c>
       <c r="B10" t="n">
-        <v>58286</v>
+        <v>57419</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>103008</v>
+        <v>102954</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ärtsångare</t>
+          <t>Enkelbeckasin</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Curruca curruca</t>
+          <t>Gallinago gallinago</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1712,6 +1712,16 @@
           <t>1</t>
         </is>
       </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M10" t="inlineStr">
         <is>
           <t>spel/sång</t>
@@ -1719,14 +1729,14 @@
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Välsviktjärnet, Vrm</t>
+          <t>Välsviken, Vrm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>419482</v>
+        <v>419198</v>
       </c>
       <c r="R10" t="n">
-        <v>6584044</v>
+        <v>6584339</v>
       </c>
       <c r="S10" t="n">
         <v>4</v>
@@ -1753,22 +1763,22 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-05-13</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>08:35</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2025-05-13</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>08:35</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1788,26 +1798,26 @@
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Sara Poppelaars</t>
+          <t>Engla Grönvall</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Karlstads Kommun - Kroppkärrsjön Fågelinventering</t>
+          <t>Karlstad Kommun - Heddiket</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129642515</t>
+          <t>https://artportalen.se/Sighting/136808909</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>101450619</v>
+        <v>136809037</v>
       </c>
       <c r="B11" t="n">
-        <v>58238</v>
+        <v>57419</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1815,21 +1825,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>103012</v>
+        <v>102954</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Grönsångare</t>
+          <t>Enkelbeckasin</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phylloscopus sibilatrix</t>
+          <t>Gallinago gallinago</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Bechstein, 1793)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1837,27 +1847,34 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr"/>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Frödingleden/cykelvägen Välsviken, Vrm</t>
+          <t>Välsviktjärnet, Vrm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>419437</v>
+        <v>418850</v>
       </c>
       <c r="R11" t="n">
-        <v>6584253</v>
+        <v>6584342</v>
       </c>
       <c r="S11" t="n">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1881,27 +1898,22 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2022-06-06</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>04:40</t>
+          <t>05:24</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2022-06-06</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>04:40</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Granskogen helt skövlad så den har flyttat till strandskogen med  al och Björk.</t>
+          <t>05:24</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1916,49 +1928,53 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Magnus Köpman</t>
+          <t>Greensway AB</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Magnus Köpman</t>
-        </is>
-      </c>
-      <c r="AY11" t="inlineStr"/>
+          <t>Engla Grönvall</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr">
+        <is>
+          <t>Karlstad Kommun - Heddiket</t>
+        </is>
+      </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/101450619</t>
+          <t>https://artportalen.se/Sighting/136809037</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>113904805</v>
+        <v>136808942</v>
       </c>
       <c r="B12" t="n">
-        <v>58327</v>
+        <v>58443</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>103015</v>
+        <v>103001</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Rödvingetrast</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Turdus iliacus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1766</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1966,6 +1982,11 @@
           <t>1</t>
         </is>
       </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
       <c r="L12" t="inlineStr">
         <is>
           <t>hane</t>
@@ -1978,17 +1999,17 @@
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Alstersnäset, Vrm</t>
+          <t>Välsviktjärnet, Vrm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>419699</v>
+        <v>418936</v>
       </c>
       <c r="R12" t="n">
-        <v>6584387</v>
+        <v>6584283</v>
       </c>
       <c r="S12" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -2012,12 +2033,22 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2023-04-18</t>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>07:04</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2023-04-18</t>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>07:04</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2037,48 +2068,48 @@
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Sara Poppelaars</t>
+          <t>Engla Grönvall</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>Karlstads kommun - NVI Reningsverk</t>
+          <t>Karlstad Kommun - Heddiket</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/113904805</t>
+          <t>https://artportalen.se/Sighting/136808942</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129642494</v>
+        <v>129642515</v>
       </c>
       <c r="B13" t="n">
-        <v>58676</v>
+        <v>58286</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>103055</v>
+        <v>103008</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Gulsparv</t>
+          <t>Ärtsångare</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Emberiza citrinella</t>
+          <t>Curruca curruca</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -2093,14 +2124,14 @@
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Välsviken, Vrm</t>
+          <t>Välsviktjärnet, Vrm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>419497</v>
+        <v>419482</v>
       </c>
       <c r="R13" t="n">
-        <v>6584277</v>
+        <v>6584044</v>
       </c>
       <c r="S13" t="n">
         <v>4</v>
@@ -2132,7 +2163,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2142,7 +2173,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2172,38 +2203,38 @@
       </c>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129642494</t>
+          <t>https://artportalen.se/Sighting/129642515</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129642514</v>
+        <v>101450619</v>
       </c>
       <c r="B14" t="n">
-        <v>58649</v>
+        <v>58238</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>103057</v>
+        <v>103012</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Sävsparv</t>
+          <t>Grönsångare</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Emberiza schoeniclus</t>
+          <t>Phylloscopus sibilatrix</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Bechstein, 1793)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -2211,24 +2242,27 @@
           <t>1</t>
         </is>
       </c>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
+          <t>permanent revir</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Välsviktjärnet, Vrm</t>
+          <t>Frödingleden/cykelvägen Välsviken, Vrm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>419456</v>
+        <v>419437</v>
       </c>
       <c r="R14" t="n">
-        <v>6584069</v>
+        <v>6584253</v>
       </c>
       <c r="S14" t="n">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2252,22 +2286,27 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-05-13</t>
+          <t>2022-06-06</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>10:46</t>
+          <t>04:40</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2025-05-13</t>
+          <t>2022-06-06</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>10:46</t>
+          <t>04:40</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Granskogen helt skövlad så den har flyttat till strandskogen med  al och Björk.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2282,31 +2321,27 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Greensway AB</t>
+          <t>Magnus Köpman</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Sara Poppelaars</t>
-        </is>
-      </c>
-      <c r="AY14" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> Karlstads Kommun - Kroppkärrsjön Fågelinventering</t>
-        </is>
-      </c>
+          <t>Magnus Köpman</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129642514</t>
+          <t>https://artportalen.se/Sighting/101450619</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>104320888</v>
+        <v>113904805</v>
       </c>
       <c r="B15" t="n">
-        <v>56823</v>
+        <v>58327</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2314,54 +2349,51 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>205992</v>
+        <v>103015</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vattenfladdermus</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Myotis daubentonii</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Kuhl, 1817)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>73</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>registreringar</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr"/>
-      <c r="N15" t="inlineStr">
-        <is>
-          <t>autobox med höghastighetsinspelning</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Söder om järnvägen intill grusväg, Vrm</t>
+          <t>Alstersnäset, Vrm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>419198</v>
+        <v>419699</v>
       </c>
       <c r="R15" t="n">
-        <v>6584321</v>
+        <v>6584387</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2385,22 +2417,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2022-07-15</t>
-        </is>
-      </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>22:11</t>
+          <t>2023-04-18</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2022-07-18</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>04:13</t>
+          <t>2023-04-18</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2415,82 +2437,78 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Åsa Duell</t>
+          <t>Greensway AB</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Åsa Duell, Andreas Mitander</t>
-        </is>
-      </c>
-      <c r="AY15" t="inlineStr"/>
+          <t>Sara Poppelaars</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr">
+        <is>
+          <t>Karlstads kommun - NVI Reningsverk</t>
+        </is>
+      </c>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/104320888</t>
+          <t>https://artportalen.se/Sighting/113904805</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>104320920</v>
+        <v>129642494</v>
       </c>
       <c r="B16" t="n">
-        <v>56835</v>
+        <v>58676</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>205995</v>
+        <v>103055</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Gulsparv</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Emberiza citrinella</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>143</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>registreringar</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr"/>
-      <c r="N16" t="inlineStr">
-        <is>
-          <t>autobox med höghastighetsinspelning</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Söder om järnvägen intill grusväg, Vrm</t>
+          <t>Välsviken, Vrm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>419198</v>
+        <v>419497</v>
       </c>
       <c r="R16" t="n">
-        <v>6584321</v>
+        <v>6584277</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2514,22 +2532,22 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2022-07-15</t>
+          <t>2025-05-13</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>22:11</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2022-07-18</t>
+          <t>2025-05-13</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>04:13</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2544,82 +2562,78 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Åsa Duell</t>
+          <t>Greensway AB</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Åsa Duell, Andreas Mitander</t>
-        </is>
-      </c>
-      <c r="AY16" t="inlineStr"/>
+          <t>Sara Poppelaars</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Karlstads Kommun - Kroppkärrsjön Fågelinventering</t>
+        </is>
+      </c>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/104320920</t>
+          <t>https://artportalen.se/Sighting/129642494</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>104320881</v>
+        <v>129642514</v>
       </c>
       <c r="B17" t="n">
-        <v>56816</v>
+        <v>58649</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>205998</v>
+        <v>103057</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Sävsparv</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Emberiza schoeniclus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>408</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>registreringar</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr"/>
-      <c r="N17" t="inlineStr">
-        <is>
-          <t>autobox med höghastighetsinspelning</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Söder om järnvägen intill grusväg, Vrm</t>
+          <t>Välsviktjärnet, Vrm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>419198</v>
+        <v>419456</v>
       </c>
       <c r="R17" t="n">
-        <v>6584321</v>
+        <v>6584069</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2643,22 +2657,22 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2022-07-15</t>
+          <t>2025-05-13</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>22:11</t>
+          <t>10:46</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2022-07-18</t>
+          <t>2025-05-13</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>04:13</t>
+          <t>10:46</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2673,16 +2687,407 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
+          <t>Greensway AB</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Sara Poppelaars</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Karlstads Kommun - Kroppkärrsjön Fågelinventering</t>
+        </is>
+      </c>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129642514</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>104320888</v>
+      </c>
+      <c r="B18" t="n">
+        <v>56823</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>205992</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Vattenfladdermus</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Myotis daubentonii</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Kuhl, 1817)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>73</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>registreringar</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr"/>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>autobox med höghastighetsinspelning</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Söder om järnvägen intill grusväg, Vrm</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>419198</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6584321</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Karlstad</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Karlstad</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2022-07-15</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>22:11</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2022-07-18</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>04:13</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
           <t>Åsa Duell</t>
         </is>
       </c>
-      <c r="AX17" t="inlineStr">
+      <c r="AX18" t="inlineStr">
         <is>
           <t>Åsa Duell, Andreas Mitander</t>
         </is>
       </c>
-      <c r="AY17" t="inlineStr"/>
-      <c r="AZ17" t="inlineStr">
+      <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104320888</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>104320920</v>
+      </c>
+      <c r="B19" t="n">
+        <v>56835</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>205995</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Dvärgpipistrell</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Pipistrellus pygmaeus</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(W.E.Leach, 1825)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>143</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>registreringar</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr"/>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>autobox med höghastighetsinspelning</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Söder om järnvägen intill grusväg, Vrm</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>419198</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6584321</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Karlstad</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Karlstad</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2022-07-15</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>22:11</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2022-07-18</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>04:13</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Åsa Duell</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Åsa Duell, Andreas Mitander</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104320920</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>104320881</v>
+      </c>
+      <c r="B20" t="n">
+        <v>56816</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>205998</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Nordfladdermus</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Eptesicus nilssonii</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>408</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>registreringar</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr"/>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>autobox med höghastighetsinspelning</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Söder om järnvägen intill grusväg, Vrm</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>419198</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6584321</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Karlstad</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Karlstad</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2022-07-15</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>22:11</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2022-07-18</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>04:13</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Åsa Duell</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Åsa Duell, Andreas Mitander</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/104320881</t>
         </is>
@@ -2706,6 +3111,9 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 14594-2022 artfynd.xlsx
+++ b/artfynd/A 14594-2022 artfynd.xlsx
@@ -1682,7 +1682,7 @@
         <v>136808909</v>
       </c>
       <c r="B10" t="n">
-        <v>57419</v>
+        <v>57432</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1817,7 +1817,7 @@
         <v>136809037</v>
       </c>
       <c r="B11" t="n">
-        <v>57419</v>
+        <v>57432</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1952,7 +1952,7 @@
         <v>136808942</v>
       </c>
       <c r="B12" t="n">
-        <v>58443</v>
+        <v>58456</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 14594-2022 artfynd.xlsx
+++ b/artfynd/A 14594-2022 artfynd.xlsx
@@ -1682,7 +1682,7 @@
         <v>136808909</v>
       </c>
       <c r="B10" t="n">
-        <v>57432</v>
+        <v>57434</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1817,7 +1817,7 @@
         <v>136809037</v>
       </c>
       <c r="B11" t="n">
-        <v>57432</v>
+        <v>57434</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1952,7 +1952,7 @@
         <v>136808942</v>
       </c>
       <c r="B12" t="n">
-        <v>58456</v>
+        <v>58458</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 14594-2022 artfynd.xlsx
+++ b/artfynd/A 14594-2022 artfynd.xlsx
@@ -1712,21 +1712,9 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Välsviken, Vrm</t>
@@ -1847,21 +1835,9 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Välsviktjärnet, Vrm</t>
@@ -1982,21 +1958,9 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Välsviktjärnet, Vrm</t>

--- a/artfynd/A 14594-2022 artfynd.xlsx
+++ b/artfynd/A 14594-2022 artfynd.xlsx
@@ -1682,7 +1682,7 @@
         <v>136808909</v>
       </c>
       <c r="B10" t="n">
-        <v>57434</v>
+        <v>57444</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1805,7 +1805,7 @@
         <v>136809037</v>
       </c>
       <c r="B11" t="n">
-        <v>57434</v>
+        <v>57444</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1928,7 +1928,7 @@
         <v>136808942</v>
       </c>
       <c r="B12" t="n">
-        <v>58458</v>
+        <v>58468</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 14594-2022 artfynd.xlsx
+++ b/artfynd/A 14594-2022 artfynd.xlsx
@@ -1682,7 +1682,7 @@
         <v>136808909</v>
       </c>
       <c r="B10" t="n">
-        <v>57444</v>
+        <v>57445</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1805,7 +1805,7 @@
         <v>136809037</v>
       </c>
       <c r="B11" t="n">
-        <v>57444</v>
+        <v>57445</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1928,7 +1928,7 @@
         <v>136808942</v>
       </c>
       <c r="B12" t="n">
-        <v>58468</v>
+        <v>58469</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 14594-2022 artfynd.xlsx
+++ b/artfynd/A 14594-2022 artfynd.xlsx
@@ -1928,7 +1928,7 @@
         <v>136808942</v>
       </c>
       <c r="B12" t="n">
-        <v>58469</v>
+        <v>58471</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
